--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-southkorea\InputData\trans\BHNVFEAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191FCD51-BA82-404D-9FC5-8A406555CEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B46915-D478-44E3-ACCF-D0338163F311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32490" yWindow="915" windowWidth="21765" windowHeight="14490" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId16"/>
+    <externalReference r:id="rId17"/>
   </externalReferences>
   <definedNames>
     <definedName name="Eno_TM">'[1]1997  Table 1a Modified'!#REF!</definedName>
@@ -120,14 +121,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="###0.00_)"/>
     <numFmt numFmtId="165" formatCode="#,##0_)"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.000000_);_(* \(#,##0.000000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.000E+00"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,8 +366,24 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -503,6 +521,12 @@
       <patternFill patternType="solid">
         <fgColor indexed="22"/>
         <bgColor indexed="55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -967,18 +991,25 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="153" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="154" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="154" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="154" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="155">
     <cellStyle name="20% - Accent1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1151,7 +1182,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Rail shipments 93-97"/>
@@ -1231,10 +1262,260 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="SYVbT-passenger"/>
+      <sheetName val="SYVbT-freight"/>
+      <sheetName val="AVLo-passengers"/>
+      <sheetName val="AVLo-freight"/>
+      <sheetName val="BAADTbVT-Passenger"/>
+      <sheetName val="BAADTbVT-Freight"/>
+      <sheetName val="BCDTRTSY_Passenger"/>
+      <sheetName val="BCDTRTSY_freight"/>
+      <sheetName val="Total_CargoDistance"/>
+      <sheetName val="Total_CargoDistance_annual"/>
+      <sheetName val="Road"/>
+      <sheetName val="Motobikes"/>
+      <sheetName val="aircraft"/>
+      <sheetName val="rail"/>
+      <sheetName val="ships"/>
+      <sheetName val="AEO 7"/>
+      <sheetName val="SYFAFE-psgr"/>
+      <sheetName val="SYFAFE-frgt"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11">
+        <row r="42">
+          <cell r="C42">
+            <v>3.4494855384074131E-4</v>
+          </cell>
+          <cell r="D42">
+            <v>4.537587230344271E-4</v>
+          </cell>
+          <cell r="E42">
+            <v>3.3955214948039873E-4</v>
+          </cell>
+          <cell r="F42">
+            <v>3.8835543291031518E-4</v>
+          </cell>
+          <cell r="G42">
+            <v>1.147549878921855E-4</v>
+          </cell>
+          <cell r="H42">
+            <v>4.3237660652546884E-4</v>
+          </cell>
+          <cell r="I42">
+            <v>1.9715881593092513E-4</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>4.3725550386066337E-4</v>
+          </cell>
+          <cell r="D43">
+            <v>5.6725587224799282E-4</v>
+          </cell>
+          <cell r="E43">
+            <v>4.3041504176466358E-4</v>
+          </cell>
+          <cell r="F43">
+            <v>5.3012016240422985E-4</v>
+          </cell>
+          <cell r="G43">
+            <v>1.454629958370202E-4</v>
+          </cell>
+          <cell r="H43">
+            <v>5.4052551857085361E-4</v>
+          </cell>
+          <cell r="I43">
+            <v>2.4647349003975621E-4</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44">
+            <v>7.2592367078105297E-5</v>
+          </cell>
+          <cell r="D44">
+            <v>1.7537305636668391E-4</v>
+          </cell>
+          <cell r="E44">
+            <v>6.4283975580087249E-5</v>
+          </cell>
+          <cell r="F44">
+            <v>1.1078813107746625E-4</v>
+          </cell>
+          <cell r="G44">
+            <v>0</v>
+          </cell>
+          <cell r="H44">
+            <v>7.6997048982108972E-5</v>
+          </cell>
+          <cell r="I44">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="C45">
+            <v>5.8062169096135046E-3</v>
+          </cell>
+          <cell r="D45">
+            <v>0</v>
+          </cell>
+          <cell r="E45">
+            <v>5.1416797805848074E-3</v>
+          </cell>
+          <cell r="F45">
+            <v>9.5424417025899051E-3</v>
+          </cell>
+          <cell r="G45">
+            <v>0</v>
+          </cell>
+          <cell r="H45">
+            <v>6.0736454453848921E-3</v>
+          </cell>
+          <cell r="I45">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="12">
+        <row r="18">
+          <cell r="D18">
+            <v>5.9831905534842047E-5</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="D19">
+            <v>5.983190553484204E-5</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="13">
+        <row r="23">
+          <cell r="C23">
+            <v>0</v>
+          </cell>
+          <cell r="D23">
+            <v>0</v>
+          </cell>
+          <cell r="E23">
+            <v>0</v>
+          </cell>
+          <cell r="F23">
+            <v>6.3999198108760673E-3</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+          <cell r="H23">
+            <v>0</v>
+          </cell>
+          <cell r="I23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>0</v>
+          </cell>
+          <cell r="D24">
+            <v>0</v>
+          </cell>
+          <cell r="E24">
+            <v>0</v>
+          </cell>
+          <cell r="F24">
+            <v>2.992789097910166E-2</v>
+          </cell>
+          <cell r="G24">
+            <v>0</v>
+          </cell>
+          <cell r="H24">
+            <v>0</v>
+          </cell>
+          <cell r="I24">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="14">
+        <row r="22">
+          <cell r="C22">
+            <v>7.8030705230531052E-4</v>
+          </cell>
+          <cell r="D22">
+            <v>0</v>
+          </cell>
+          <cell r="E22">
+            <v>0</v>
+          </cell>
+          <cell r="F22">
+            <v>5.5294125429859176E-3</v>
+          </cell>
+          <cell r="G22">
+            <v>0</v>
+          </cell>
+          <cell r="H22">
+            <v>0</v>
+          </cell>
+          <cell r="I22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23">
+            <v>1.0021251453207708E-3</v>
+          </cell>
+          <cell r="D23">
+            <v>0</v>
+          </cell>
+          <cell r="E23">
+            <v>0</v>
+          </cell>
+          <cell r="F23">
+            <v>1.6108650602655154E-2</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+          <cell r="H23">
+            <v>0</v>
+          </cell>
+          <cell r="I23">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1272,9 +1553,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1307,26 +1588,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1359,26 +1623,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1552,11 +1799,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="107.42578125" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="107.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1575,31 +1822,8 @@
     <row r="5" spans="1:2">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="4"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="4"/>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="4"/>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="4"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="4"/>
-    </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1611,15 +1835,15 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -2107,7 +2331,7 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>5.5294125429859176E-3</v>
       </c>
       <c r="C5" s="3">
@@ -2494,166 +2718,167 @@
         <v>14</v>
       </c>
       <c r="B8" s="3">
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6588237628957749E-2</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
     </row>
     <row r="13" spans="1:35">
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="8"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="8"/>
-      <c r="AF13" s="8"/>
-      <c r="AG13" s="8"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="6"/>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="6"/>
+      <c r="AG13" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2664,13 +2889,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -3545,132 +3770,133 @@
         <v>14</v>
       </c>
       <c r="B8" s="3">
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3">
         <f t="shared" si="0"/>
-        <v>4.832595180796545E-2</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3681,14 +3907,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -3791,127 +4017,127 @@
       </c>
       <c r="B2" s="3">
         <f t="array" ref="B2:B8">TRANSPOSE('SYFAFE-psgr'!B6:H6)</f>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="C2" s="3">
         <f>B2</f>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="D2" s="3">
         <f t="shared" ref="D2:AF8" si="0">C2</f>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="E2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="G2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="I2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="J2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="K2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="L2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="M2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="N2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="O2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="P2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="Q2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="R2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="S2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="T2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="U2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="V2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="W2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="X2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="Y2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="Z2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="AA2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="AB2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="AC2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="AD2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="AE2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="AF2" s="3">
         <f t="shared" si="0"/>
-        <v>1.02207161101318E-3</v>
+        <v>3.2293482418666772E-5</v>
       </c>
       <c r="AH2" s="3"/>
       <c r="AI2" s="3"/>
@@ -4049,127 +4275,127 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="M4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="O4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="P4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="Q4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="R4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="V4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="W4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="X4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="Y4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="Z4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="AA4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="AB4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="AC4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="AD4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="AE4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
       <c r="AF4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0049397002369564E-5</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -4177,127 +4403,127 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="1"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="O5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="P5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="T5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="U5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="V5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="W5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="X5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="Z5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="AA5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="AB5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="AC5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="AD5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="AE5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="AF5" s="3">
         <f t="shared" si="0"/>
-        <v>3.1805809143661031E-4</v>
+        <v>1.0049397002369565E-5</v>
       </c>
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
@@ -4563,132 +4789,133 @@
         <v>14</v>
       </c>
       <c r="B8" s="3">
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="V8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="W8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="Z8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="AA8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="AB8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="AC8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="AD8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="AF8" s="3">
         <f t="shared" si="0"/>
-        <v>9.5417427430983083E-4</v>
+        <v>3.0148191007108693E-5</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4699,13 +4926,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -4808,127 +5035,127 @@
       </c>
       <c r="B2" s="3">
         <f t="array" ref="B2:B8">TRANSPOSE('SYFAFE-frgt'!B6:H6)</f>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="C2" s="3">
         <f>B2</f>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="D2" s="3">
         <f t="shared" ref="D2:AF8" si="0">C2</f>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="E2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="G2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="I2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="J2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="K2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="L2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="M2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="N2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="O2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="P2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="Q2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="R2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="S2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="T2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="U2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="V2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="W2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="X2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="Y2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="Z2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="AA2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="AB2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="AC2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="AD2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="AE2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="AF2" s="3">
         <f t="shared" si="0"/>
-        <v>1.1521530229677897E-2</v>
+        <v>1.5467626362604087E-2</v>
       </c>
       <c r="AH2" s="3"/>
       <c r="AI2" s="3"/>
@@ -4938,127 +5165,127 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:R8" si="1">B3</f>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="D3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="E3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="J3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="K3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="L3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="M3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="N3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="O3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="P3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="Q3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="R3" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="S3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="T3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="U3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="V3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="W3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="X3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="Y3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="Z3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AA3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AB3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AC3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AD3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AE3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AF3" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.813365E-3</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -5066,127 +5293,127 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="1"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="M4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="O4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="P4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="Q4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="R4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="V4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="W4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="X4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="Y4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="Z4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AA4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AB4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AC4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AD4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AE4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AF4" s="3">
         <f t="shared" si="0"/>
-        <v>3.2499077185230334E-3</v>
+        <v>4.813365E-3</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -5194,127 +5421,127 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="1"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="O5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="P5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="T5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="U5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="V5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="W5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="X5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="Z5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AA5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AB5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AC5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AD5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AE5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AF5" s="3">
         <f t="shared" si="0"/>
-        <v>3.5853807852542999E-3</v>
+        <v>4.813365E-3</v>
       </c>
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
@@ -5580,132 +5807,133 @@
         <v>14</v>
       </c>
       <c r="B8" s="3">
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="V8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="W8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="Z8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="AA8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="AB8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="AC8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="AD8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="AF8" s="3">
         <f t="shared" si="0"/>
-        <v>1.0756142355762898E-2</v>
+        <v>1.4440094999999998E-2</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5716,13 +5944,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -5825,127 +6053,127 @@
       </c>
       <c r="B2" s="3">
         <f t="array" ref="B2:B8">TRANSPOSE('SYFAFE-psgr'!B7:H7)</f>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3">
         <f>B2</f>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3">
         <f t="shared" ref="D2:AF8" si="0">C2</f>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="K2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="P2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="R2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="T2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="U2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="V2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="W2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="X2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="3">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="3"/>
       <c r="AI2" s="3"/>
@@ -6085,127 +6313,127 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="1"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="M4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="O4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="P4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="Q4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="R4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="V4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="W4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="X4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="Y4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="Z4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AA4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AB4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AC4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AD4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AE4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AF4" s="3">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
@@ -6605,132 +6833,133 @@
         <v>14</v>
       </c>
       <c r="B8" s="3">
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6741,13 +6970,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:32">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -6850,127 +7079,127 @@
       </c>
       <c r="B2">
         <f t="array" ref="B2:B8">TRANSPOSE('SYFAFE-frgt'!B7:H7)</f>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <f>B2</f>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f t="shared" ref="D2:AF8" si="0">C2</f>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="T2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="U2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="V2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="W2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="X2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="Y2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="Z2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AA2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AB2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AD2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
       <c r="AF2">
         <f t="shared" si="0"/>
-        <v>1.8103029084840444E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -7106,127 +7335,127 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="C4">
         <f t="shared" si="1"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="J4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="L4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="P4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="Q4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="S4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="T4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="U4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="V4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="W4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="X4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="Y4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="Z4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AA4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AB4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AC4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AD4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AE4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AF4">
         <f t="shared" si="0"/>
-        <v>5.6334750108537641E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -7618,162 +7847,173 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="W8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="Y8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="Z8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AB8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AC8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AD8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
       <c r="AF8">
         <f t="shared" si="0"/>
-        <v>1.6900425032561291E-4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5608C21D-4939-4BB5-83B1-F132ABBAD71C}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" ht="28.8">
+      <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7781,191 +8021,267 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
-        <v>3.0396698208103967E-4</v>
-      </c>
-      <c r="C2">
-        <v>2.3957201310558667E-4</v>
-      </c>
-      <c r="D2">
-        <v>2.4836534211036528E-4</v>
-      </c>
-      <c r="E2">
-        <v>2.3887516512595359E-4</v>
-      </c>
-      <c r="F2">
-        <v>1.8402941893909386E-4</v>
-      </c>
-      <c r="G2">
-        <v>2.6963351337436545E-4</v>
-      </c>
-      <c r="H2">
-        <v>2.212283607775526E-4</v>
+      <c r="B2" s="3">
+        <f>[2]Road!C42</f>
+        <v>3.4494855384074131E-4</v>
+      </c>
+      <c r="C2" s="3">
+        <f>[2]Road!D42</f>
+        <v>4.537587230344271E-4</v>
+      </c>
+      <c r="D2" s="3">
+        <f>[2]Road!E42</f>
+        <v>3.3955214948039873E-4</v>
+      </c>
+      <c r="E2" s="3">
+        <f>[2]Road!F42</f>
+        <v>3.8835543291031518E-4</v>
+      </c>
+      <c r="F2" s="3">
+        <f>[2]Road!G42</f>
+        <v>1.147549878921855E-4</v>
+      </c>
+      <c r="G2" s="3">
+        <f>[2]Road!H42</f>
+        <v>4.3237660652546884E-4</v>
+      </c>
+      <c r="H2" s="3">
+        <f>[2]Road!I42</f>
+        <v>1.9715881593092513E-4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>2.7692774003548483E-3</v>
-      </c>
-      <c r="C3">
-        <v>2.141719453609167E-3</v>
-      </c>
-      <c r="D3">
-        <v>2.2513573503928309E-3</v>
-      </c>
-      <c r="E3">
-        <v>2.3317845655879865E-3</v>
-      </c>
-      <c r="F3">
-        <v>1.668171498875807E-3</v>
-      </c>
-      <c r="G3">
-        <v>2.4104624469818738E-3</v>
-      </c>
-      <c r="H3">
-        <v>1.9777313627970783E-3</v>
+      <c r="B3" s="3">
+        <f>[2]Road!C43</f>
+        <v>4.3725550386066337E-4</v>
+      </c>
+      <c r="C3" s="3">
+        <f>[2]Road!D43</f>
+        <v>5.6725587224799282E-4</v>
+      </c>
+      <c r="D3" s="3">
+        <f>[2]Road!E43</f>
+        <v>4.3041504176466358E-4</v>
+      </c>
+      <c r="E3" s="3">
+        <f>[2]Road!F43</f>
+        <v>5.3012016240422985E-4</v>
+      </c>
+      <c r="F3" s="3">
+        <f>[2]Road!G43</f>
+        <v>1.454629958370202E-4</v>
+      </c>
+      <c r="G3" s="3">
+        <f>[2]Road!H43</f>
+        <v>5.4052551857085361E-4</v>
+      </c>
+      <c r="H3" s="3">
+        <f>[2]Road!I43</f>
+        <v>2.4647349003975621E-4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>2.05659800129969E-2</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
+      <c r="B4" s="3">
+        <f>[2]aircraft!C23</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <f>[2]aircraft!D23</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <f>[2]aircraft!E23</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <f>[2]aircraft!F23</f>
         <v>6.3999198108760673E-3</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>1.9199759432628197E-2</v>
+      <c r="F4" s="3">
+        <f>[2]aircraft!G23</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <f>[2]aircraft!H23</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <f>[2]aircraft!I23</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
+        <f>[2]rail!C22</f>
         <v>7.8030705230531052E-4</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
+      <c r="C5" s="3">
+        <f>[2]rail!D22</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <f>[2]rail!E22</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <f>[2]rail!F22</f>
         <v>5.5294125429859176E-3</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>1.6588237628957749E-2</v>
+      <c r="F5" s="3">
+        <f>[2]rail!G22</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <f>[2]rail!H22</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <f>[2]rail!I22</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6">
-        <v>1.02207161101318E-3</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>3.1805809143661031E-4</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>9.5417427430983083E-4</v>
+      <c r="B6" s="3">
+        <v>3.2293482418666772E-5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1.0049397002369564E-5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.0049397002369565E-5</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>3.0148191007108693E-5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7">
-        <v>1.8103029084840444E-4</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>5.6334750108537641E-5</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>1.6900425032561291E-4</v>
-      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <f>[2]Motobikes!D18</f>
+        <v>5.9831905534842047E-5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D3F229-11AA-46C5-A65C-D98510BBA29C}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" ht="28.8">
+      <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7973,159 +8289,198 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
-        <v>1.9185271653600656E-5</v>
-      </c>
-      <c r="C2">
-        <v>1.3762562068887589E-4</v>
-      </c>
-      <c r="D2">
-        <v>7.4066882935860471E-5</v>
-      </c>
-      <c r="E2">
-        <v>1.0749560153660953E-4</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1.3753680882406556E-4</v>
-      </c>
-      <c r="H2">
-        <v>3.2248680460982855E-4</v>
+      <c r="B2" s="3">
+        <f>[2]Road!C44</f>
+        <v>7.2592367078105297E-5</v>
+      </c>
+      <c r="C2" s="3">
+        <f>[2]Road!D44</f>
+        <v>1.7537305636668391E-4</v>
+      </c>
+      <c r="D2" s="3">
+        <f>[2]Road!E44</f>
+        <v>6.4283975580087249E-5</v>
+      </c>
+      <c r="E2" s="3">
+        <f>[2]Road!F44</f>
+        <v>1.1078813107746625E-4</v>
+      </c>
+      <c r="F2" s="3">
+        <f>[2]Road!G44</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <f>[2]Road!H44</f>
+        <v>7.6997048982108972E-5</v>
+      </c>
+      <c r="H2" s="3">
+        <f>[2]Road!I44</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="E3">
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="H3">
-        <v>2.7162025918871339E-2</v>
+      <c r="B3" s="3">
+        <f>[2]Road!C45</f>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="C3" s="3">
+        <f>[2]Road!D45</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <f>[2]Road!E45</f>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="E3" s="3">
+        <f>[2]Road!F45</f>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="F3" s="3">
+        <f>[2]Road!G45</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <f>[2]Road!H45</f>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="H3" s="3">
+        <f>[2]Road!I45</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>9.6172518702715024E-2</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
+      <c r="B4" s="3">
+        <f>[2]aircraft!C24</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <f>[2]aircraft!D24</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <f>[2]aircraft!E24</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <f>[2]aircraft!F24</f>
         <v>2.992789097910166E-2</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>8.9783672937304965E-2</v>
+      <c r="F4" s="3">
+        <f>[2]aircraft!G24</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <f>[2]aircraft!H24</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <f>[2]aircraft!I24</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
+        <f>[2]rail!C23</f>
         <v>1.0021251453207708E-3</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
+      <c r="C5" s="3">
+        <f>[2]rail!D23</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <f>[2]rail!E23</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <f>[2]rail!F23</f>
         <v>1.6108650602655154E-2</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>4.832595180796545E-2</v>
+      <c r="F5" s="3">
+        <f>[2]rail!G23</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <f>[2]rail!H23</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <f>[2]rail!I23</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6">
-        <v>1.1521530229677897E-2</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>3.2499077185230334E-3</v>
-      </c>
-      <c r="E6">
-        <v>3.5853807852542999E-3</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>1.0756142355762898E-2</v>
+      <c r="B6" s="3">
+        <v>1.5467626362604087E-2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4.813365E-3</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4.813365E-3</v>
+      </c>
+      <c r="E6" s="11">
+        <v>4.813365E-3</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1.4440094999999998E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7">
-        <v>1.8103029084840444E-4</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>5.6334750108537641E-5</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>1.6900425032561291E-4</v>
-      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <f>[2]Motobikes!D19</f>
+        <v>5.983190553484204E-5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8136,13 +8491,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -8245,127 +8600,127 @@
       </c>
       <c r="B2" s="3">
         <f t="array" ref="B2:B8">TRANSPOSE('SYFAFE-psgr'!B2:H2)</f>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="C2" s="3">
         <f>B2</f>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="D2" s="3">
         <f t="shared" ref="D2:AF8" si="0">C2</f>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="E2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="G2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="I2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="J2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="K2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="L2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="M2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="N2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="O2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="P2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="Q2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="R2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="S2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="T2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="U2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="V2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="W2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="X2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="Y2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="Z2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="AA2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="AB2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="AC2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="AD2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="AE2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="AF2" s="3">
         <f t="shared" si="0"/>
-        <v>3.0396698208103967E-4</v>
+        <v>3.4494855384074131E-4</v>
       </c>
       <c r="AH2" s="3"/>
       <c r="AI2" s="3"/>
@@ -8375,127 +8730,127 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:R8" si="1">B3</f>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="D3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="E3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="J3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="K3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="L3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="M3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="N3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="O3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="P3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="Q3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="R3" s="3">
         <f t="shared" si="1"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="S3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="T3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="U3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="V3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="W3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="X3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="Y3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="Z3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="AA3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="AB3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="AC3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="AD3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="AE3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="AF3" s="3">
         <f t="shared" si="0"/>
-        <v>2.3957201310558667E-4</v>
+        <v>4.537587230344271E-4</v>
       </c>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
@@ -8504,258 +8859,258 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
-        <v>2.4836534211036528E-4</v>
+      <c r="B4" s="3">
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="1"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="M4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="O4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="P4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="Q4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="R4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="V4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="W4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="X4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="Y4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="Z4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="AA4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="AB4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="AC4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="AD4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="AE4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
+        <v>3.3955214948039873E-4</v>
       </c>
       <c r="AF4" s="3">
         <f t="shared" si="0"/>
-        <v>2.4836534211036528E-4</v>
-      </c>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="6"/>
+        <v>3.3955214948039873E-4</v>
+      </c>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
     </row>
     <row r="5" spans="1:35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="1"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="O5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="P5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="T5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="U5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="V5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="W5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="X5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="Z5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="AA5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="AB5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="AC5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="AD5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="AE5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="AF5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3887516512595359E-4</v>
+        <v>3.8835543291031518E-4</v>
       </c>
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
@@ -8765,127 +9120,127 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="1"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="F6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="M6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="N6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="O6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="P6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="Q6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="R6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="S6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="T6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="U6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="V6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="W6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="X6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="Z6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="AA6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="AB6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="AC6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="AD6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="AE6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="AF6" s="3">
         <f t="shared" si="0"/>
-        <v>1.8402941893909386E-4</v>
+        <v>1.147549878921855E-4</v>
       </c>
       <c r="AH6" s="3"/>
       <c r="AI6" s="3"/>
@@ -8895,127 +9250,127 @@
         <v>13</v>
       </c>
       <c r="B7" s="3">
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="1"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="F7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="J7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="N7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="O7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="P7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="Q7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="R7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="S7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="T7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="U7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="V7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="W7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="X7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="Z7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="AA7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="AB7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="AC7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="AD7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="AE7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="AF7" s="3">
         <f t="shared" si="0"/>
-        <v>2.6963351337436545E-4</v>
+        <v>4.3237660652546884E-4</v>
       </c>
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
@@ -9025,127 +9380,127 @@
         <v>14</v>
       </c>
       <c r="B8" s="3">
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="V8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="W8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="Z8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="AA8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="AB8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="AC8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="AD8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="AF8" s="3">
         <f t="shared" si="0"/>
-        <v>2.212283607775526E-4</v>
+        <v>1.9715881593092513E-4</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
@@ -9186,6 +9541,7 @@
       <c r="AH10" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9196,13 +9552,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -9305,127 +9661,127 @@
       </c>
       <c r="B2" s="3">
         <f t="array" ref="B2:B8">TRANSPOSE('SYFAFE-frgt'!B2:H2)</f>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="C2" s="3">
         <f>B2</f>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="D2" s="3">
         <f t="shared" ref="D2:AF8" si="0">C2</f>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="E2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="G2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="I2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="J2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="K2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="L2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="M2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="N2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="O2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="P2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="Q2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="R2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="S2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="T2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="U2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="V2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="W2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="X2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="Y2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="Z2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="AA2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="AB2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="AC2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="AD2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="AE2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="AF2" s="3">
         <f t="shared" si="0"/>
-        <v>1.9185271653600656E-5</v>
+        <v>7.2592367078105297E-5</v>
       </c>
       <c r="AH2" s="3"/>
       <c r="AI2" s="3"/>
@@ -9435,127 +9791,127 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:R8" si="1">B3</f>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="D3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="E3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="J3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="K3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="L3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="M3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="N3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="O3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="P3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="Q3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="R3" s="3">
         <f t="shared" si="1"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="S3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="T3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="U3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="V3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="W3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="X3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="Y3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="Z3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="AA3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="AB3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="AC3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="AD3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="AE3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="AF3" s="3">
         <f t="shared" si="0"/>
-        <v>1.3762562068887589E-4</v>
+        <v>1.7537305636668391E-4</v>
       </c>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
@@ -9565,127 +9921,127 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="1"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="M4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="O4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="P4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="Q4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="R4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="V4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="W4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="X4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="Y4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="Z4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="AA4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="AB4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="AC4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="AD4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="AE4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="AF4" s="3">
         <f t="shared" si="0"/>
-        <v>7.4066882935860471E-5</v>
+        <v>6.4283975580087249E-5</v>
       </c>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
@@ -9695,127 +10051,127 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="1"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="O5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="P5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="T5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="U5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="V5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="W5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="X5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="Z5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="AA5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="AB5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="AC5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="AD5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="AE5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="AF5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0749560153660953E-4</v>
+        <v>1.1078813107746625E-4</v>
       </c>
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
@@ -9955,127 +10311,127 @@
         <v>13</v>
       </c>
       <c r="B7" s="3">
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="1"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="F7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="J7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="N7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="O7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="P7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="Q7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="R7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="S7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="T7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="U7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="V7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="W7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="X7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="Z7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="AA7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="AB7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="AC7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="AD7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="AE7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="AF7" s="3">
         <f t="shared" si="0"/>
-        <v>1.3753680882406556E-4</v>
+        <v>7.6997048982108972E-5</v>
       </c>
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
@@ -10084,133 +10440,134 @@
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="6">
-        <v>3.2248680460982855E-4</v>
-      </c>
-      <c r="C8" s="6">
-        <f t="shared" si="1"/>
-        <v>3.2248680460982855E-4</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
-      </c>
-      <c r="E8" s="6">
-        <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3">
         <f t="shared" si="0"/>
-        <v>3.2248680460982855E-4</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10221,13 +10578,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -10330,127 +10687,127 @@
       </c>
       <c r="B2" s="3">
         <f t="array" ref="B2:B8">TRANSPOSE('SYFAFE-psgr'!B3:H3)</f>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="C2" s="3">
         <f>B2</f>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="D2" s="3">
         <f t="shared" ref="D2:AF8" si="0">C2</f>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="E2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="G2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="I2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="J2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="K2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="L2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="M2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="N2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="O2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="P2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="Q2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="R2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="S2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="T2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="U2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="V2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="W2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="X2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="Y2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="Z2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="AA2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="AB2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="AC2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="AD2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="AE2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="AF2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7692774003548483E-3</v>
+        <v>4.3725550386066337E-4</v>
       </c>
       <c r="AH2" s="3"/>
       <c r="AI2" s="3"/>
@@ -10460,127 +10817,127 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:R8" si="1">B3</f>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="D3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="E3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="J3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="K3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="L3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="M3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="N3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="O3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="P3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="Q3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="R3" s="3">
         <f t="shared" si="1"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="S3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="T3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="U3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="V3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="W3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="X3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="Y3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="Z3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="AA3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="AB3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="AC3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="AD3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="AE3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="AF3" s="3">
         <f t="shared" si="0"/>
-        <v>2.141719453609167E-3</v>
+        <v>5.6725587224799282E-4</v>
       </c>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
@@ -10590,127 +10947,127 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="1"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="M4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="O4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="P4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="Q4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="R4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="V4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="W4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="X4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="Y4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="Z4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="AA4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="AB4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="AC4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="AD4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="AE4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="AF4" s="3">
         <f t="shared" si="0"/>
-        <v>2.2513573503928309E-3</v>
+        <v>4.3041504176466358E-4</v>
       </c>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
@@ -10720,127 +11077,127 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="1"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="O5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="P5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="T5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="U5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="V5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="W5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="X5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="Z5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="AA5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="AB5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="AC5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="AD5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="AE5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="AF5" s="3">
         <f t="shared" si="0"/>
-        <v>2.3317845655879865E-3</v>
+        <v>5.3012016240422985E-4</v>
       </c>
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
@@ -10850,127 +11207,127 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="1"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="F6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="M6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="N6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="O6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="P6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="Q6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="R6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="S6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="T6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="U6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="V6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="W6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="X6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="Z6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="AA6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="AB6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="AC6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="AD6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="AE6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="AF6" s="3">
         <f t="shared" si="0"/>
-        <v>1.668171498875807E-3</v>
+        <v>1.454629958370202E-4</v>
       </c>
       <c r="AH6" s="3"/>
       <c r="AI6" s="3"/>
@@ -10980,127 +11337,127 @@
         <v>13</v>
       </c>
       <c r="B7" s="3">
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="1"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="F7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="J7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="N7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="O7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="P7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="Q7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="R7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="S7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="T7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="U7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="V7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="W7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="X7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="Z7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="AA7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="AB7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="AC7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="AD7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="AE7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="AF7" s="3">
         <f t="shared" si="0"/>
-        <v>2.4104624469818738E-3</v>
+        <v>5.4052551857085361E-4</v>
       </c>
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
@@ -11110,132 +11467,133 @@
         <v>14</v>
       </c>
       <c r="B8" s="3">
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="V8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="W8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="Z8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="AA8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="AB8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="AC8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="AD8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="AF8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9777313627970783E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11246,13 +11604,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -11353,129 +11711,129 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="3">
         <f t="array" ref="B2:B8">TRANSPOSE('SYFAFE-frgt'!B3:H3)</f>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="C2" s="6">
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="C2" s="3">
         <f>B2</f>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="D2" s="6">
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="D2" s="3">
         <f t="shared" ref="D2:AF8" si="0">C2</f>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="E2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="F2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="G2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="H2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="I2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="J2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="K2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="L2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="M2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="N2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="O2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="P2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="Q2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="R2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="S2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="T2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="U2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="V2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="W2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="X2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="Y2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="Z2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="AA2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="AB2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="AC2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="AD2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="AE2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
-      </c>
-      <c r="AF2" s="6">
-        <f t="shared" si="0"/>
-        <v>1.5005628221864591E-3</v>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="E2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="F2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="G2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="H2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="I2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="J2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="K2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="L2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="M2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="N2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="O2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="P2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="Q2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="R2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="S2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="T2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="U2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="V2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="W2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="X2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="Y2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="Z2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="AA2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="AB2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="AC2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="AD2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="AE2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="AF2" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8062169096135046E-3</v>
       </c>
       <c r="AH2" s="3"/>
       <c r="AI2" s="3"/>
@@ -11487,123 +11845,123 @@
       <c r="B3" s="3">
         <v>0</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <f t="shared" ref="C3:R8" si="1">B3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R3" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE3" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AF3" s="6">
+      <c r="D3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF3" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11615,127 +11973,127 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="C4" s="6">
-        <f t="shared" si="1"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="D4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="E4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="F4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="G4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="H4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="I4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="J4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="K4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="L4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="M4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="N4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="O4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="P4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="Q4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="R4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="S4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="T4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="U4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="V4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="W4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="X4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="Y4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="Z4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="AA4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="AB4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="AC4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="AD4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="AE4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
-      </c>
-      <c r="AF4" s="6">
-        <f t="shared" si="0"/>
-        <v>5.7930902879829681E-3</v>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="C4" s="3">
+        <f t="shared" si="1"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="G4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="H4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="J4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="K4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="L4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="M4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="N4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="O4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="P4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="Q4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="R4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="S4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="T4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="U4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="V4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="W4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="X4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="Y4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="Z4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="AA4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="AB4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="AC4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="AD4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="AE4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="AF4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1416797805848074E-3</v>
       </c>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
@@ -11745,127 +12103,127 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="C5" s="6">
-        <f t="shared" si="1"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="E5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="F5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="G5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="H5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="I5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="J5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="K5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="L5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="M5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="N5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="O5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="P5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="Q5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="R5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="S5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="T5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="U5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="V5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="W5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="X5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="Y5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="Z5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="AA5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="AB5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="AC5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="AD5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="AE5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
-      </c>
-      <c r="AF5" s="6">
-        <f t="shared" si="0"/>
-        <v>9.0540086396237816E-3</v>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="C5" s="3">
+        <f t="shared" si="1"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="H5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="J5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="K5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="L5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="M5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="N5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="O5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="P5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="Q5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="R5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="S5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="T5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="U5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="V5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="W5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="X5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="Z5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="AA5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="AB5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="AC5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="AD5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="AE5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="AF5" s="3">
+        <f t="shared" si="0"/>
+        <v>9.5424417025899051E-3</v>
       </c>
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
@@ -11877,123 +12235,123 @@
       <c r="B6" s="3">
         <v>0</v>
       </c>
-      <c r="C6" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AF6" s="6">
+      <c r="C6" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -12005,127 +12363,127 @@
         <v>13</v>
       </c>
       <c r="B7" s="3">
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="C7" s="6">
-        <f t="shared" si="1"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="D7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="E7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="F7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="G7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="H7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="I7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="J7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="K7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="L7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="M7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="N7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="O7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="P7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="Q7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="R7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="S7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="T7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="U7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="V7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="W7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="X7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="Y7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="Z7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="AA7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="AB7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="AC7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="AD7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="AE7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
-      </c>
-      <c r="AF7" s="6">
-        <f t="shared" si="0"/>
-        <v>1.0609092351245585E-2</v>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="J7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="K7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="L7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="M7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="N7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="O7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="P7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="Q7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="R7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="S7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="T7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="U7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="V7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="W7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="X7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="Z7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="AA7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="AB7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="AC7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="AD7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="AE7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="AF7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0736454453848921E-3</v>
       </c>
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
@@ -12135,132 +12493,133 @@
         <v>14</v>
       </c>
       <c r="B8" s="3">
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="C8" s="6">
-        <f t="shared" si="1"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="E8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="F8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="G8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="H8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="I8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="J8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="K8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="L8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="M8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="N8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="O8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="P8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="Q8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="R8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="S8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="T8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="U8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="V8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="W8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="X8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="Y8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="Z8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="AA8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="AB8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="AC8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="AD8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="AE8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
-      </c>
-      <c r="AF8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7162025918871339E-2</v>
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12271,13 +12630,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -12380,127 +12739,127 @@
       </c>
       <c r="B2" s="3">
         <f t="array" ref="B2:B8">TRANSPOSE('SYFAFE-psgr'!B4:H4)</f>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3">
         <f>B2</f>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3">
         <f t="shared" ref="D2:AF8" si="0">C2</f>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="P2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="R2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="T2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="U2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="V2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="W2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="X2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="3">
         <f t="shared" si="0"/>
-        <v>2.05659800129969E-2</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="3"/>
       <c r="AI2" s="3"/>
@@ -13152,132 +13511,133 @@
         <v>14</v>
       </c>
       <c r="B8" s="3">
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3">
         <f t="shared" si="0"/>
-        <v>1.9199759432628197E-2</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13288,13 +13648,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:35">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B1">
@@ -13397,127 +13757,127 @@
       </c>
       <c r="B2" s="3">
         <f t="array" ref="B2:B8">TRANSPOSE('SYFAFE-frgt'!B4:H4)</f>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3">
         <f>B2</f>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3">
         <f t="shared" ref="D2:AF8" si="0">C2</f>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="P2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="R2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="T2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="U2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="V2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="W2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="X2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="3">
         <f t="shared" si="0"/>
-        <v>9.6172518702715024E-2</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="3"/>
       <c r="AI2" s="3"/>
@@ -14169,132 +14529,133 @@
         <v>14</v>
       </c>
       <c r="B8" s="3">
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3">
         <f t="shared" si="0"/>
-        <v>8.9783672937304965E-2</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14444,6 +14805,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -14452,20 +14819,37 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB6CFF06-B83B-4A00-9CDB-43AF6F18358B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB6CFF06-B83B-4A00-9CDB-43AF6F18358B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34B8507D-2FDC-44A3-815A-86B4815488A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ADC4865-734B-4090-93A2-62178E7C1923}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ADC4865-734B-4090-93A2-62178E7C1923}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34B8507D-2FDC-44A3-815A-86B4815488A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\trans\BHNVFEAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B46915-D478-44E3-ACCF-D0338163F311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA058888-C78D-483F-ADF0-78F5156E3061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32490" yWindow="915" windowWidth="21765" windowHeight="14490" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-33555" yWindow="-1320" windowWidth="28800" windowHeight="15225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1800,10 +1800,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" customWidth="1"/>
-    <col min="2" max="2" width="107.33203125" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" customWidth="1"/>
+    <col min="2" max="2" width="107.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1835,11 +1835,11 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -2889,9 +2889,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -3907,10 +3907,10 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -4926,9 +4926,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -5944,9 +5944,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -6970,9 +6970,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -7979,19 +7979,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5608C21D-4939-4BB5-83B1-F132ABBAD71C}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8">
+    <row r="1" spans="1:8" ht="29">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -8247,19 +8247,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D3F229-11AA-46C5-A65C-D98510BBA29C}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.44140625" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8">
+    <row r="1" spans="1:8" ht="29">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
@@ -8491,9 +8491,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -9552,9 +9552,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -10578,9 +10578,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -11604,9 +11604,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -12630,9 +12630,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -13648,9 +13648,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -14661,6 +14661,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -14804,22 +14819,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34B8507D-2FDC-44A3-815A-86B4815488A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ADC4865-734B-4090-93A2-62178E7C1923}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB6CFF06-B83B-4A00-9CDB-43AF6F18358B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14835,21 +14852,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ADC4865-734B-4090-93A2-62178E7C1923}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34B8507D-2FDC-44A3-815A-86B4815488A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>